--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444666370446814</v>
       </c>
       <c r="C2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>27662683</v>
+        <v>4272650</v>
       </c>
       <c r="L2" t="n">
-        <v>16107925</v>
+        <v>2191554</v>
       </c>
       <c r="M2" t="n">
-        <v>4042188</v>
+        <v>492116</v>
       </c>
       <c r="N2" t="n">
-        <v>213929</v>
+        <v>16552</v>
       </c>
       <c r="O2" t="n">
-        <v>2398870</v>
+        <v>300497</v>
       </c>
       <c r="P2" t="n">
-        <v>953040</v>
+        <v>120655</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999921321868896</v>
+        <v>0.9999843835830688</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9043293595314026</v>
+        <v>0.8223313093185425</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8055564165115356</v>
+        <v>0.6641060709953308</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7579917311668396</v>
+        <v>0.5762839913368225</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5024484992027283</v>
+        <v>0.1830993741750717</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8061496615409851</v>
+        <v>0.6405410170555115</v>
       </c>
       <c r="W2" t="n">
-        <v>0.86799156665802</v>
+        <v>0.752860963344574</v>
       </c>
       <c r="X2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.95653235912323</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911312997341156</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580047488212585</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.66214919090271</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646644592285</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024449655927808</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>27662683</v>
+        <v>4272650</v>
       </c>
       <c r="E3" t="n">
-        <v>2650099</v>
+        <v>752850</v>
       </c>
       <c r="F3" t="n">
-        <v>43669</v>
+        <v>17663</v>
       </c>
       <c r="G3" t="n">
-        <v>4716</v>
+        <v>1420</v>
       </c>
       <c r="H3" t="n">
-        <v>2235</v>
+        <v>947</v>
       </c>
       <c r="I3" t="n">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="J3" t="n">
-        <v>60417421</v>
+        <v>10069521</v>
       </c>
       <c r="K3" t="n">
-        <v>65205964</v>
+        <v>10447293</v>
       </c>
       <c r="L3" t="n">
-        <v>74913147</v>
+        <v>12012338</v>
       </c>
       <c r="M3" t="n">
-        <v>91598969</v>
+        <v>15118278</v>
       </c>
       <c r="N3" t="n">
-        <v>97748072</v>
+        <v>16252649</v>
       </c>
       <c r="O3" t="n">
-        <v>94862310</v>
+        <v>15737372</v>
       </c>
       <c r="P3" t="n">
-        <v>97191032</v>
+        <v>16182953</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9110490083694458</v>
+        <v>0.8468104600906372</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8178789019584656</v>
+        <v>0.6650726199150085</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7209876775741577</v>
+        <v>0.5258262157440186</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3990587294101715</v>
+        <v>0.1849302798509598</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7847530245780945</v>
+        <v>0.5892155766487122</v>
       </c>
       <c r="W3" t="n">
-        <v>0.821568489074707</v>
+        <v>0.6237334609031677</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1194510</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51498</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>40960</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60417720</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66811145</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>77057112</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>92093936</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>97778931</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95139602</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>97256450</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575998783111572</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099897742271423</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574815392494202</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616687178611755</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015793204307556</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319545241795172</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2759670</v>
+        <v>867992</v>
       </c>
       <c r="E4" t="n">
-        <v>16107925</v>
+        <v>2191554</v>
       </c>
       <c r="F4" t="n">
-        <v>744946</v>
+        <v>203914</v>
       </c>
       <c r="G4" t="n">
-        <v>23663</v>
+        <v>9411</v>
       </c>
       <c r="H4" t="n">
-        <v>53972</v>
+        <v>20428</v>
       </c>
       <c r="I4" t="n">
-        <v>4576</v>
+        <v>1910</v>
       </c>
       <c r="J4" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="K4" t="n">
-        <v>2926486</v>
+        <v>923127</v>
       </c>
       <c r="L4" t="n">
-        <v>3888098</v>
+        <v>1108452</v>
       </c>
       <c r="M4" t="n">
-        <v>1290572</v>
+        <v>361831</v>
       </c>
       <c r="N4" t="n">
-        <v>211844</v>
+        <v>73847</v>
       </c>
       <c r="O4" t="n">
-        <v>576843</v>
+        <v>168633</v>
       </c>
       <c r="P4" t="n">
-        <v>144943</v>
+        <v>39607</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999960660934448</v>
+        <v>0.9999921917915344</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9076766967773438</v>
+        <v>0.8343913555145264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8116708993911743</v>
+        <v>0.664588987827301</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7390268445014954</v>
+        <v>0.5499000549316406</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4448249638080597</v>
+        <v>0.1840102821588516</v>
       </c>
       <c r="V4" t="n">
-        <v>0.795307457447052</v>
+        <v>0.613807201385498</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8441422581672668</v>
+        <v>0.6822410225868225</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1233664</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>498690</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>33091</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6876</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1321305</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1744133</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>795605</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>180985</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299551</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570658206939697</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910650908946991</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577430844306946</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619088649749756</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017719030380249</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>106252</v>
+        <v>38103</v>
       </c>
       <c r="E5" t="n">
-        <v>1065455</v>
+        <v>297033</v>
       </c>
       <c r="F5" t="n">
-        <v>4042188</v>
+        <v>492116</v>
       </c>
       <c r="G5" t="n">
-        <v>77696</v>
+        <v>23652</v>
       </c>
       <c r="H5" t="n">
-        <v>292012</v>
+        <v>76708</v>
       </c>
       <c r="I5" t="n">
-        <v>22845</v>
+        <v>8274</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2700867</v>
+        <v>772930</v>
       </c>
       <c r="L5" t="n">
-        <v>3586830</v>
+        <v>1103656</v>
       </c>
       <c r="M5" t="n">
-        <v>1564271</v>
+        <v>443775</v>
       </c>
       <c r="N5" t="n">
-        <v>322155</v>
+        <v>72952</v>
       </c>
       <c r="O5" t="n">
-        <v>657977</v>
+        <v>209498</v>
       </c>
       <c r="P5" t="n">
-        <v>206985</v>
+        <v>72785</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999969601631165</v>
+        <v>0.9999939799308777</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9428672194480896</v>
+        <v>0.8966826796531677</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9241093397140503</v>
+        <v>0.8652468323707581</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9710156321525574</v>
+        <v>0.9509255886077881</v>
       </c>
       <c r="U5" t="n">
-        <v>0.99457848072052</v>
+        <v>0.9910575747489929</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9874632358551025</v>
+        <v>0.9769657254219055</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9964269995689392</v>
+        <v>0.9931535124778748</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48367</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>512041</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59802</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>175016</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1287418</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1772729</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>799024</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181374</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300857</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735144376754761</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642943739891052</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838101863861084</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210821151733</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939042329788208</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983834028244019</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>58710</v>
+        <v>15656</v>
       </c>
       <c r="E6" t="n">
-        <v>90819</v>
+        <v>20768</v>
       </c>
       <c r="F6" t="n">
-        <v>119393</v>
+        <v>25035</v>
       </c>
       <c r="G6" t="n">
-        <v>213929</v>
+        <v>16552</v>
       </c>
       <c r="H6" t="n">
-        <v>48606</v>
+        <v>10266</v>
       </c>
       <c r="I6" t="n">
-        <v>4550</v>
+        <v>1213</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38939</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32230</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65403</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41916</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1720</v>
+        <v>1339</v>
       </c>
       <c r="E7" t="n">
-        <v>77243</v>
+        <v>35394</v>
       </c>
       <c r="F7" t="n">
-        <v>366901</v>
+        <v>108432</v>
       </c>
       <c r="G7" t="n">
-        <v>99258</v>
+        <v>36166</v>
       </c>
       <c r="H7" t="n">
-        <v>2398870</v>
+        <v>300497</v>
       </c>
       <c r="I7" t="n">
-        <v>112835</v>
+        <v>28164</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4866</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>178032</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45539</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="D8" t="n">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>4482</v>
+        <v>2407</v>
       </c>
       <c r="F8" t="n">
-        <v>15663</v>
+        <v>6787</v>
       </c>
       <c r="G8" t="n">
-        <v>6511</v>
+        <v>3198</v>
       </c>
       <c r="H8" t="n">
-        <v>180018</v>
+        <v>60284</v>
       </c>
       <c r="I8" t="n">
-        <v>953040</v>
+        <v>120655</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
